--- a/QCM4_4_PHY.xlsx
+++ b/QCM4_4_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10169A2-E3BF-49FF-8DC5-D87D061B9EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6EF210-67EC-463F-9CF5-8DCA3A477057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="130">
   <si>
     <t>Question</t>
   </si>
@@ -394,20 +394,31 @@
   </si>
   <si>
     <t>Une masse m : Une masse m, considérée ponctuelle, est lancée de A avec une vitesse initiale $\vec{v}_0 = v_0\vec{i}$. Elle parcourt d'abord la portion horizontale $AB = d$ puis s'engage sur un plan incliné d'un angle $\alpha$ par rapport à l'horizontale. En outre m subit dès le départ et sur tout son trajet, une force de frottement de type $\vec{F} = -F\vec{u}$ où F est une constante et $\vec{u}$ un vecteur unitaire colinéaire au vecteur vitesse. On note $g$ l'accélération de la pesanteur.
-&lt;img src="/images/PHY_QCM1_4_Q7.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
  $v_0 = 4\text{ m.s}^{-1} ; m = 100\text{ g} ; d = 7\text{ m} ; F = 0,05\text{ N} ; g = 10\text{ m.s}^{-2} ; \sin \alpha = 0,1$.</t>
   </si>
   <si>
-    <t>Un mouvement rectiligne : Un mobile est animé d'un mouvement rectiligne. Sa vitesse est représentée figure 1.
-&lt;img src="/images/PHY_QCM1_4_Q8.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
-    <t>Un plan Incliné : On considère un solide de masse $m$ posé sur un plan incliné d'un angle $\alpha = 30^\circ$ par rapport à l'horizontale. Ce solide est sous l'action de son poids $P$, de la réaction du plan incliné $R$. Les frottements sont supposées négligeables. À $t = 0$, le solide est lancé depuis l'origine selon l'axe $(O, x)$.
-&lt;img src="/images/PHY_QCM1_4_Q9.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
-    <t>Travail et énergie : Le jeu de curling se pratique sur une patinoire horizontale. Le joueur pousse le palet initialement immobile puis le lâche dans l'objectif de lui faire atteindre une cible. Pour cela, il exerce pendant $4\text{ s}$ une force constante $F$ suivant une trajectoire rectiligne. Le palet possède une énergie cinétique de $40\text{ J}$ au moment où le joueur lâche le palet. Le palet a une masse de $20\text{ kg}$.
-&lt;img src="/images/PHY_QCM1_4_Q10.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+    <t xml:space="preserve">Un mouvement rectiligne : Un mobile est animé d'un mouvement rectiligne. Sa vitesse est représentée figure 1.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un plan Incliné : On considère un solide de masse $m$ posé sur un plan incliné d'un angle $\alpha = 30^\circ$ par rapport à l'horizontale. Ce solide est sous l'action de son poids $P$, de la réaction du plan incliné $R$. Les frottements sont supposées négligeables. À $t = 0$, le solide est lancé depuis l'origine selon l'axe $(O, x)$.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travail et énergie : Le jeu de curling se pratique sur une patinoire horizontale. Le joueur pousse le palet initialement immobile puis le lâche dans l'objectif de lui faire atteindre une cible. Pour cela, il exerce pendant $4\text{ s}$ une force constante $F$ suivant une trajectoire rectiligne. Le palet possède une énergie cinétique de $40\text{ J}$ au moment où le joueur lâche le palet. Le palet a une masse de $20\text{ kg}$.
+</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q7.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q8.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q9.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q10.png</t>
   </si>
 </sst>
 </file>
@@ -919,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="204" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="178.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>122</v>
       </c>
@@ -946,6 +957,9 @@
       </c>
       <c r="I2" s="11" t="s">
         <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1185,7 +1199,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>123</v>
       </c>
@@ -1212,6 +1226,9 @@
       </c>
       <c r="I12" s="10" t="s">
         <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1314,7 +1331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="102" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>124</v>
       </c>
@@ -1342,8 +1359,11 @@
       <c r="I17" s="7" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
+      <c r="J17" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>125</v>
       </c>
@@ -1371,8 +1391,11 @@
       <c r="I18" s="7" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="J18" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B19" s="8" t="s">
         <v>111</v>
       </c>
@@ -1398,7 +1421,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>80</v>
       </c>
@@ -1427,7 +1450,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>85</v>
       </c>
@@ -1456,7 +1479,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
         <v>114</v>
       </c>

--- a/QCM4_4_PHY.xlsx
+++ b/QCM4_4_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6EF210-67EC-463F-9CF5-8DCA3A477057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C084838D-1D3C-470A-8238-92EFBFE8D225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="130">
   <si>
     <t>Question</t>
   </si>
@@ -90,24 +90,9 @@
     <t>$4\text{ m.s}^{-1}$</t>
   </si>
   <si>
-    <t>À déterminer (graphique)</t>
-  </si>
-  <si>
-    <t>À déterminer</t>
-  </si>
-  <si>
-    <t>$11,75\text{ s}$</t>
-  </si>
-  <si>
     <t>$12\text{ s}$</t>
   </si>
   <si>
-    <t>$12,25\text{ s}$</t>
-  </si>
-  <si>
-    <t>$12,5\text{ s}$</t>
-  </si>
-  <si>
     <t>$2,75\text{ s}$</t>
   </si>
   <si>
@@ -129,9 +114,6 @@
     <t>$0,5\text{ m.s}^{-1}$</t>
   </si>
   <si>
-    <t>Une piste circulaire : Un coureur parcourt une piste circulaire (ABCDA). Il part de A sans vitesse initiale et parcourt le premier quart de la piste avec une vitesse dont la norme augmente proportionnellement au temps soit $v=k_1.t$. Il parcourt le reste avec un mouvement circulaire uniforme, c'est-à-dire à la vitesse atteinte en B. Le rayon du cercle est $R=\frac{300}{\pi}$ mètres et $k_1=\frac{1}{3}\text{ m.s}^{-2}$.</t>
-  </si>
-  <si>
     <t>$20\text{ s}$</t>
   </si>
   <si>
@@ -240,9 +222,6 @@
     <t>$150\text{ m}$</t>
   </si>
   <si>
-    <t>$5\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
     <t>$v_0 = 1\text{ m.s}^{-1}$</t>
   </si>
   <si>
@@ -267,9 +246,6 @@
     <t>$a = 4\text{ m.s}^{-2}$</t>
   </si>
   <si>
-    <t>Le palet parcourt une distance $d = 40\text{ m}$ avant de s'arrêter dans la cible.</t>
-  </si>
-  <si>
     <t>constante</t>
   </si>
   <si>
@@ -282,9 +258,6 @@
     <t>diminue</t>
   </si>
   <si>
-    <t>L'énergie mécanique diminue du travail des frottements.</t>
-  </si>
-  <si>
     <t>la variation de l'énergie cinétique</t>
   </si>
   <si>
@@ -357,18 +330,9 @@
     <t>A quelle vitesse initiale minimale $v_0$ faut-il lancer le solide pour atteindre le point A, $x_A = 2,5\text{ m}$ ? On prend $g = 10\text{ m.s}^{-2}$.</t>
   </si>
   <si>
-    <t>La vitesse atteinte par le palet à la fin de la poussée vaut :</t>
-  </si>
-  <si>
     <t>L'accélération pendant la phase de poussée vaut :</t>
   </si>
   <si>
-    <t>L'énergie mécanique est :</t>
-  </si>
-  <si>
-    <t>Le travail des frottements est égal à :</t>
-  </si>
-  <si>
     <t>La force de frottement a pour valeur :</t>
   </si>
   <si>
@@ -393,32 +357,75 @@
     <t>$50\text{ cm}$</t>
   </si>
   <si>
-    <t>Une masse m : Une masse m, considérée ponctuelle, est lancée de A avec une vitesse initiale $\vec{v}_0 = v_0\vec{i}$. Elle parcourt d'abord la portion horizontale $AB = d$ puis s'engage sur un plan incliné d'un angle $\alpha$ par rapport à l'horizontale. En outre m subit dès le départ et sur tout son trajet, une force de frottement de type $\vec{F} = -F\vec{u}$ où F est une constante et $\vec{u}$ un vecteur unitaire colinéaire au vecteur vitesse. On note $g$ l'accélération de la pesanteur.
+    <t>PHY_QCM1_4_Q7.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q8.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q9.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q10.png</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Une masse m : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Une masse m, considérée ponctuelle, est lancée de A avec une vitesse initiale $\vec{v}_0 = v_0\vec{i}$. Elle parcourt d'abord la portion horizontale $AB = d$ puis s'engage sur un plan incliné d'un angle $\alpha$ par rapport à l'horizontale. En outre m subit dès le départ et sur tout son trajet, une force de frottement de type $\vec{F} = -F\vec{u}$ où F est une constante et $\vec{u}$ un vecteur unitaire colinéaire au vecteur vitesse. On note $g$ l'accélération de la pesanteur.
  $v_0 = 4\text{ m.s}^{-1} ; m = 100\text{ g} ; d = 7\text{ m} ; F = 0,05\text{ N} ; g = 10\text{ m.s}^{-2} ; \sin \alpha = 0,1$.</t>
   </si>
   <si>
-    <t xml:space="preserve">Un mouvement rectiligne : Un mobile est animé d'un mouvement rectiligne. Sa vitesse est représentée figure 1.
+    <t>$1,75\text{ s}$</t>
+  </si>
+  <si>
+    <t>$2,25\text{ s}$</t>
+  </si>
+  <si>
+    <t>$2,5\text{ s}$</t>
+  </si>
+  <si>
+    <t>&gt;center&gt;&lt;b&gt;Une piste circulaire : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Un coureur parcourt une piste circulaire (ABCDA). Il part de A sans vitesse initiale et parcourt le premier quart de la piste avec une vitesse dont la norme augmente proportionnellement au temps soit $v=k_1.t$. Il parcourt le reste avec un mouvement circulaire uniforme, c'est-à-dire à la vitesse atteinte en B. Le rayon du cercle est $R=\frac{300}{\pi}$ mètres et $k_1=\frac{1}{3}\text{ m.s}^{-2}$.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Un mouvement rectiligne : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Un mobile est animé d'un mouvement rectiligne. Sa vitesse est représentée figure 1.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Un plan Incliné : On considère un solide de masse $m$ posé sur un plan incliné d'un angle $\alpha = 30^\circ$ par rapport à l'horizontale. Ce solide est sous l'action de son poids $P$, de la réaction du plan incliné $R$. Les frottements sont supposées négligeables. À $t = 0$, le solide est lancé depuis l'origine selon l'axe $(O, x)$.
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Un plan Incliné : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;On considère un solide de masse $m$ posé sur un plan incliné d'un angle $\alpha = 30^\circ$ par rapport à l'horizontale. Ce solide est sous l'action de son poids $\vecP$, de la réaction du plan incliné $\vecR$. Les frottements sont supposées négligeables. À $t = 0$, le solide est lancé depuis l'origine selon l'axe $(O, x)$.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Travail et énergie : Le jeu de curling se pratique sur une patinoire horizontale. Le joueur pousse le palet initialement immobile puis le lâche dans l'objectif de lui faire atteindre une cible. Pour cela, il exerce pendant $4\text{ s}$ une force constante $F$ suivant une trajectoire rectiligne. Le palet possède une énergie cinétique de $40\text{ J}$ au moment où le joueur lâche le palet. Le palet a une masse de $20\text{ kg}$.
+    <t>$v_0 = 1,5\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$v_0 = 2,8\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$v_0 = 3,1\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$v_0 = 5,0\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$v_0 = 6,2\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Travail et énergie : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Le jeu de curling se pratique sur une patinoire horizontale. Le joueur pousse le palet initialement immobile puis le lâche dans l'objectif de lui faire atteindre une cible. Pour cela, il exerce pendant $4\text{ s}$ une force constante $F$ suivant une trajectoire rectiligne. Le palet possède une énergie cinétique de $40\text{ J}$ au moment où le joueur lâche le palet. Le palet a une masse de $20\text{ kg}$.
 </t>
   </si>
   <si>
-    <t>PHY_QCM1_4_Q7.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_4_Q8.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_4_Q9.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_4_Q10.png</t>
+    <t>La vitesse atteinte par le palet à la fin de la phase de poussée vaut :</t>
+  </si>
+  <si>
+    <t>Le palet parcourt une distance $d = 40\text{ m}$ avant de s'arrêter dans la cible.
+L'énergie mécanique est :</t>
+  </si>
+  <si>
+    <t>L'énergie mécanique diminue du travail des frottements.
+Le travail des frottements est égal à :</t>
   </si>
 </sst>
 </file>
@@ -930,12 +937,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="178.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
@@ -955,100 +962,96 @@
       <c r="H2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="I2" s="11"/>
       <c r="J2" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>24</v>
-      </c>
       <c r="F3" s="9" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>22</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>17</v>
@@ -1060,215 +1063,211 @@
         <v>19</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>38</v>
-      </c>
       <c r="I7" s="7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="F12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="G12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="51" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>62</v>
-      </c>
       <c r="H12" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>21</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I12" s="10"/>
       <c r="J12" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>21</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>15</v>
@@ -1276,128 +1275,124 @@
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>21</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="10"/>
+    </row>
+    <row r="17" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="140.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="G18" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="H18" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="102" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="J17" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="I18" s="7" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J18" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B19" s="8" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>3</v>
@@ -1406,103 +1401,99 @@
         <v>13</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>14</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>80</v>
-      </c>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
       <c r="B20" s="8" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>85</v>
-      </c>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
       <c r="B21" s="8" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/QCM4_4_PHY.xlsx
+++ b/QCM4_4_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C084838D-1D3C-470A-8238-92EFBFE8D225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F418CA9D-BE6B-4857-BFA9-C3B420BE6E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="130">
   <si>
     <t>Question</t>
   </si>
@@ -962,7 +962,9 @@
       <c r="H2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="11"/>
+      <c r="I2" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="J2" t="s">
         <v>110</v>
       </c>
@@ -990,7 +992,7 @@
         <v>22</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
@@ -1041,7 +1043,9 @@
       <c r="H5" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="I5" s="10"/>
+      <c r="I5" s="7" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
@@ -1066,7 +1070,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="140.25" x14ac:dyDescent="0.25">
@@ -1227,7 +1231,9 @@
       <c r="H12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="10"/>
+      <c r="I12" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="J12" t="s">
         <v>111</v>
       </c>
@@ -1254,7 +1260,9 @@
       <c r="H13" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="11"/>
+      <c r="I13" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
@@ -1300,7 +1308,9 @@
       <c r="H15" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="11"/>
+      <c r="I15" s="9" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
@@ -1324,7 +1334,9 @@
       <c r="H16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="10"/>
+      <c r="I16" s="7" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
